--- a/artfynd/A 60681-2025 artfynd.xlsx
+++ b/artfynd/A 60681-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119644991</v>
+        <v>119644998</v>
       </c>
       <c r="B2" t="n">
-        <v>58013</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +710,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435674</v>
+        <v>435780</v>
       </c>
       <c r="R2" t="n">
-        <v>6289597</v>
+        <v>6289619</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:31</t>
+          <t>05:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:31</t>
+          <t>05:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,6 +793,127 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>119644991</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Boarp södra, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>435674</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6289597</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Södra Ljunga</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>05:31</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>05:31</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Filip Myllyaho</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Filip Myllyaho</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60681-2025 artfynd.xlsx
+++ b/artfynd/A 60681-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119644998</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,8 +924,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119644991</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>